--- a/data/trending_integrated_20261013_13.xlsx
+++ b/data/trending_integrated_20261013_13.xlsx
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11110</v>
+        <v>8780</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+30.86%</t>
+          <t>'+29.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.92</v>
+        <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>401</v>
+        <v>279</v>
       </c>
       <c r="H2" t="n">
-        <v>15.64</v>
+        <v>1.84</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8490</v>
+        <v>6760</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7530</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>7250</v>
       </c>
       <c r="N2" t="n">
-        <v>14.72</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>331074000000</v>
+        <v>87579099850</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>-176000</v>
+        <v>-105000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남클러스터 외 테마 소멸 및 주가 급등락 속 주포의 매집 추정. 금일 상한가 예상.</t>
+          <t>독보적인 상승 추세 및 10년간 움직이지 않던 자리 돌파, 광주 경제자유구역 확대 수혜 기대감 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남클러스터', '주포', '상한가']</t>
+          <t>['텐버거', '경제자유구역', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8780</v>
+        <v>17440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.88%</t>
+          <t>'+6.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.57</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>273</v>
+        <v>158</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6760</v>
+        <v>16350</v>
       </c>
       <c r="K3" t="n">
-        <v>7530</v>
+        <v>15790</v>
       </c>
       <c r="L3" t="n">
-        <v>8780</v>
+        <v>19930</v>
       </c>
       <c r="M3" t="n">
-        <v>7250</v>
+        <v>15520</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>87556965470</v>
+        <v>238227112600</v>
       </c>
       <c r="P3" t="n">
-        <v>10300</v>
+        <v>19930</v>
       </c>
       <c r="Q3" t="n">
-        <v>952</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-105000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>독보적인 상승 추세 및 10년간 움직이지 않던 자리 돌파, 광주 경제자유구역 확대 수혜 기대감 언급.</t>
+          <t>보안 기술의 중요성과 함께 주가 상승에 대한 기대가 나타난다. 미국 보안주 폭락 및 글로벌 경기 침체 우려도 언급된다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['텐버거', '경제자유구역', '대장주']</t>
+          <t>['보안 기술', '주가 상승', '경기 침체']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17180</v>
+        <v>11740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.08%</t>
+          <t>'+6.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>153</v>
+        <v>425</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K4" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L4" t="n">
-        <v>19930</v>
+        <v>13970</v>
       </c>
       <c r="M4" t="n">
-        <v>15520</v>
+        <v>10810</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>235833379805</v>
+        <v>346296767705</v>
       </c>
       <c r="P4" t="n">
-        <v>19930</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-176000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>보안주 상승 및 신고가 경신 기대감, AI 기술 발전과 보안 중요성 강조.</t>
+          <t>개인 투자자들의 매도와 매수에 대한 엇갈린 의견이 존재하며, 일부는 주포의 움직임을 주시하고 있다. 테마의 영향력 약화 및 주가 변동성에 대한 언급이 있다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', 'AI']</t>
+          <t>['주포', '테마', '물갈이']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3765</v>
+        <v>3725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.48%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H5" t="n">
         <v>0.91</v>
@@ -886,7 +886,7 @@
         <v>0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>86868283109</v>
+        <v>87993113069</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>녹십자엠에스, 페스트 및 독감 관련 이슈로 인한 주가 상승 기대감. 대세 상승 시작 및 변종 바이러스 우려.</t>
+          <t>신규 질병 발생 가능성에 대한 언급과 함께 주가 상승에 대한 기대가 존재한다. 페스트, 독감 등 질병 관련 뉴스가 주가 변동의 주요 요인으로 작용하고 있다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['페스트', '독감', '대세 상승']</t>
+          <t>['질병', '주가 상승', '뉴스']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13210</v>
+        <v>1565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13410</v>
+        <v>1578</v>
       </c>
       <c r="K6" t="n">
-        <v>13260</v>
+        <v>1578</v>
       </c>
       <c r="L6" t="n">
-        <v>14580</v>
+        <v>1776</v>
       </c>
       <c r="M6" t="n">
-        <v>12920</v>
+        <v>1457</v>
       </c>
       <c r="N6" t="n">
-        <v>0.21</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>62745100845</v>
+        <v>8998939078</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>2930</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>910</v>
       </c>
       <c r="R6" t="n">
         <v>34000</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 좌절감과 함께 매수세 대비 매도세 우위, 종가 하락 예상 등 부정적 전망.</t>
+          <t>경제자유구역 추가 편입 및 메가프로젝트 투자에 대한 긍정적인 전망이 있다. 주가 상승에 대한 기대감과 함께 일부 투자자 간의 의견 대립이 관찰된다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['매도세', '주가 하락', '종가']</t>
+          <t>['경제자유구역', '투자', '주가 상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43550</v>
+        <v>13170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'-1.79%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F7" t="n">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>683</v>
+        <v>248</v>
       </c>
       <c r="H7" t="n">
-        <v>13.1</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>44400</v>
+        <v>13410</v>
       </c>
       <c r="K7" t="n">
-        <v>43300</v>
+        <v>13260</v>
       </c>
       <c r="L7" t="n">
-        <v>44100</v>
+        <v>14580</v>
       </c>
       <c r="M7" t="n">
-        <v>42250</v>
+        <v>12920</v>
       </c>
       <c r="N7" t="n">
-        <v>13.33</v>
+        <v>0.21</v>
       </c>
       <c r="O7" t="n">
-        <v>24689757000</v>
+        <v>63208617305</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>34000</v>
       </c>
       <c r="S7" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>간암 1차 승인 시 주가 상승 기대감, 공매도 세력 및 악성 매물대 소화 필요. 통합 IR 데이 일정 언급.</t>
+          <t>주가 하락에 대한 좌절감과 함께 매수세 대비 매도세 우위, 종가 하락 예상 등 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['간암 1차 승인', '공매도', 'IR 데이']</t>
+          <t>['매도세', '주가 하락', '종가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17550</v>
+        <v>43550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-1.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="G8" t="n">
-        <v>295</v>
+        <v>692</v>
       </c>
       <c r="H8" t="n">
-        <v>27.69</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18010</v>
+        <v>44400</v>
       </c>
       <c r="K8" t="n">
-        <v>17430</v>
+        <v>43300</v>
       </c>
       <c r="L8" t="n">
-        <v>17840</v>
+        <v>44100</v>
       </c>
       <c r="M8" t="n">
-        <v>17210</v>
+        <v>42250</v>
       </c>
       <c r="N8" t="n">
-        <v>27.61</v>
+        <v>13.33</v>
       </c>
       <c r="O8" t="n">
-        <v>52463255955</v>
+        <v>25269078975</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>681000</v>
+        <v>45000</v>
       </c>
       <c r="S8" t="n">
-        <v>71000</v>
+        <v>7000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
+          <t>신약 승인 및 임상 결과에 대한 기대감이 존재하며, 공매도 세력에 대한 언급이 있다. 주가 상승 가능성과 악재 반영 여부에 대한 논의가 진행 중이다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '목표가']</t>
+          <t>['신약 승인', '공매도', '임상 결과']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18040</v>
+        <v>17650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.42</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>88</v>
+        <v>297</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46</v>
+        <v>27.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18550</v>
+        <v>18010</v>
       </c>
       <c r="K9" t="n">
-        <v>17550</v>
+        <v>17430</v>
       </c>
       <c r="L9" t="n">
-        <v>19580</v>
+        <v>17840</v>
       </c>
       <c r="M9" t="n">
-        <v>17010</v>
+        <v>17210</v>
       </c>
       <c r="N9" t="n">
-        <v>0.88</v>
+        <v>27.61</v>
       </c>
       <c r="O9" t="n">
-        <v>71308809190</v>
+        <v>53699335045</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>17210</v>
       </c>
       <c r="R9" t="n">
-        <v>-65000</v>
+        <v>681000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내 해킹 이슈 및 보안주 강세 흐름 속에서 엑스게이트 주가 급등 기대감 표출. 매집 의혹 및 추가 상승 전망.</t>
+          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '급등']</t>
+          <t>['FLNG', '매출 전망', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15600</v>
+        <v>18110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-2.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.16</v>
+        <v>-0.42</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>363</v>
+        <v>88</v>
       </c>
       <c r="H10" t="n">
-        <v>9.630000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16090</v>
+        <v>18550</v>
       </c>
       <c r="K10" t="n">
-        <v>15190</v>
+        <v>17550</v>
       </c>
       <c r="L10" t="n">
-        <v>15980</v>
+        <v>19580</v>
       </c>
       <c r="M10" t="n">
-        <v>15100</v>
+        <v>17010</v>
       </c>
       <c r="N10" t="n">
-        <v>9.470000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="O10" t="n">
-        <v>49635061920</v>
+        <v>71584210210</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R10" t="n">
-        <v>395000</v>
+        <v>-65000</v>
       </c>
       <c r="S10" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>금감원 사모펀드 점검 및 주가 하락 우려, 공매도 관련 언급. 15000원 이탈 및 연말 2만원 목표.</t>
+          <t>국내 해킹 이슈 및 보안주 강세 흐름 속에서 엑스게이트 주가 급등 기대감 표출. 매집 의혹 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금감원', '공매도', '주가 하락']</t>
+          <t>['해킹', '보안주', '급등']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,169 +1384,169 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5990</v>
+        <v>15660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-2.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E11" t="n">
+        <v>146</v>
+      </c>
+      <c r="F11" t="n">
         <v>63</v>
       </c>
-      <c r="F11" t="n">
-        <v>23</v>
-      </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>377</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6210</v>
+        <v>16090</v>
       </c>
       <c r="K11" t="n">
-        <v>5950</v>
+        <v>15190</v>
       </c>
       <c r="L11" t="n">
-        <v>6560</v>
+        <v>15980</v>
       </c>
       <c r="M11" t="n">
-        <v>5840</v>
+        <v>15100</v>
       </c>
       <c r="N11" t="n">
-        <v>0.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>22777135835</v>
+        <v>50636799200</v>
       </c>
       <c r="P11" t="n">
-        <v>11370</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-5000</v>
+        <v>395000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>주가 하락에 대한 우려와 함께 공매도 및 대차해지에 대한 논의가 있다. 건설주 전반의 부진과 국내 증시 상황에 대한 부정적인 인식이 나타난다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['공매도', '대차해지', '증시 상황']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68800</v>
+        <v>6030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>235</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>728</v>
+        <v>124</v>
       </c>
       <c r="H12" t="n">
-        <v>22.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>71500</v>
+        <v>6210</v>
       </c>
       <c r="K12" t="n">
-        <v>68400</v>
+        <v>5950</v>
       </c>
       <c r="L12" t="n">
-        <v>70600</v>
+        <v>6560</v>
       </c>
       <c r="M12" t="n">
-        <v>67300</v>
+        <v>5840</v>
       </c>
       <c r="N12" t="n">
-        <v>22.21</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>137073281300</v>
+        <v>22958570035</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>225000</v>
+        <v>-5000</v>
       </c>
       <c r="S12" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 부양 실패 및 도박판 비유, 특정 정치인 비난과 함께 반대매매 및 주가 하락 가능성 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['도박판', '반대매매', '주가 하락']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,82 +1563,82 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1517</v>
+        <v>69200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="G13" t="n">
-        <v>221</v>
+        <v>732</v>
       </c>
       <c r="H13" t="n">
-        <v>0.32</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1578</v>
+        <v>71500</v>
       </c>
       <c r="K13" t="n">
-        <v>1578</v>
+        <v>68400</v>
       </c>
       <c r="L13" t="n">
-        <v>1776</v>
+        <v>70600</v>
       </c>
       <c r="M13" t="n">
-        <v>1457</v>
+        <v>67300</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>8928817008</v>
+        <v>140460293350</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>34000</v>
+        <v>225000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
+          <t>주가 부양 실패 및 도박판 비유, 특정 정치인 비난과 함께 반대매매 및 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['경제자유구역', '전국구', '수혜주']</t>
+          <t>['도박판', '반대매매', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7400</v>
+        <v>7450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="H14" t="n">
         <v>26.01</v>
@@ -1714,7 +1714,7 @@
         <v>26.37</v>
       </c>
       <c r="O14" t="n">
-        <v>21508129040</v>
+        <v>22080822745</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6460</v>
+        <v>6490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.14%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="H15" t="n">
         <v>12.27</v>
@@ -1806,7 +1806,7 @@
         <v>12.57</v>
       </c>
       <c r="O15" t="n">
-        <v>19559785825</v>
+        <v>19786520525</v>
       </c>
       <c r="P15" t="n">
         <v>8850</v>
@@ -1898,7 +1898,7 @@
         <v>3.37</v>
       </c>
       <c r="O16" t="n">
-        <v>73423515990</v>
+        <v>74756849400</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 확인, 주가 상승 추세 전망. 미국 AI 거품론 언급.</t>
+          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '외인 매수', '주가 상승']</t>
+          <t>['어닝서프라이즈', '외인매수', '공장']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6830</v>
+        <v>6880</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.83%</t>
+          <t>'-7.15%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F17" t="n">
         <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H17" t="n">
         <v>1.8</v>
@@ -1990,7 +1990,7 @@
         <v>1.99</v>
       </c>
       <c r="O17" t="n">
-        <v>65005019940</v>
+        <v>65380850220</v>
       </c>
       <c r="P17" t="n">
         <v>23500</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>171900</v>
+        <v>12440</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.98%</t>
+          <t>'-7.16%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>-1.01</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="G18" t="n">
-        <v>122</v>
+        <v>366</v>
       </c>
       <c r="H18" t="n">
-        <v>75.20999999999999</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>186800</v>
+        <v>13400</v>
       </c>
       <c r="K18" t="n">
-        <v>180800</v>
+        <v>13750</v>
       </c>
       <c r="L18" t="n">
-        <v>183000</v>
+        <v>15390</v>
       </c>
       <c r="M18" t="n">
-        <v>170000</v>
+        <v>11980</v>
       </c>
       <c r="N18" t="n">
-        <v>75.23</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
-        <v>559152001200</v>
+        <v>187819858250</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>70400</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-173000</v>
+        <v>-76000</v>
       </c>
       <c r="S18" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>주가 상승에 대한 기대와 공매도에 대한 우려가 혼재되어 있으며, 일부 투자자는 목표가를 제시하고 있다. 최근 주가 흐름에 대한 부정적인 인식이 있다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['공매도', '목표가', '주가 흐름']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>230000</v>
+        <v>172800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.18%</t>
+          <t>'-7.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
-        <v>569</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>1841</v>
+        <v>127</v>
       </c>
       <c r="H19" t="n">
-        <v>46.3</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>250500</v>
+        <v>186800</v>
       </c>
       <c r="K19" t="n">
-        <v>241500</v>
+        <v>180800</v>
       </c>
       <c r="L19" t="n">
-        <v>244000</v>
+        <v>183000</v>
       </c>
       <c r="M19" t="n">
-        <v>228000</v>
+        <v>170000</v>
       </c>
       <c r="N19" t="n">
-        <v>46.35</v>
+        <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3567307938000</v>
+        <v>570766249300</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q19" t="n">
-        <v>90200</v>
+        <v>70400</v>
       </c>
       <c r="R19" t="n">
-        <v>-2204000</v>
+        <v>-173000</v>
       </c>
       <c r="S19" t="n">
-        <v>241000</v>
+        <v>65000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 중국 반도체 경쟁력 언급과 함께 주가 하락 전망.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,51 +2199,51 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '주가 하락']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1457000</v>
+        <v>231000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.22%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E20" t="n">
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G20" t="n">
-        <v>1839</v>
+        <v>1769</v>
       </c>
       <c r="H20" t="n">
-        <v>49.41</v>
+        <v>46.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1605000</v>
+        <v>250500</v>
       </c>
       <c r="K20" t="n">
-        <v>1538000</v>
+        <v>241500</v>
       </c>
       <c r="L20" t="n">
-        <v>1554000</v>
+        <v>244000</v>
       </c>
       <c r="M20" t="n">
-        <v>1445000</v>
+        <v>228000</v>
       </c>
       <c r="N20" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4700470849000</v>
+        <v>3638738664250</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R20" t="n">
-        <v>-722000</v>
+        <v>-2204000</v>
       </c>
       <c r="S20" t="n">
-        <v>88000</v>
+        <v>241000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 주가 하락 및 손실 언급. 민주당 지지자 및 이재명 관련 부정적 언급.</t>
+          <t>정치적 발언 및 특정 지역에 대한 부정적인 의견이 주를 이루며, 정부 정책 및 리더십에 대한 비판이 제기되고 있다. 반도체 공장 설립 관련 논란도 언급된다.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치', '주가 하락', '손실']</t>
+          <t>['정부 정책', '반도체', '지역갈등']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12100</v>
+        <v>1457000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-9.70%</t>
+          <t>'-9.22%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>157</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>569</v>
       </c>
       <c r="G21" t="n">
-        <v>389</v>
+        <v>1891</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>49.41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13400</v>
+        <v>1605000</v>
       </c>
       <c r="K21" t="n">
-        <v>13750</v>
+        <v>1538000</v>
       </c>
       <c r="L21" t="n">
-        <v>15390</v>
+        <v>1554000</v>
       </c>
       <c r="M21" t="n">
-        <v>11980</v>
+        <v>1445000</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>49.52</v>
       </c>
       <c r="O21" t="n">
-        <v>185345255635</v>
+        <v>4810698052500</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>403000</v>
       </c>
       <c r="R21" t="n">
-        <v>-76000</v>
+        <v>-722000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>공매도 세력의 주가 누르기와 외인 매도세 언급, 목표가 15000원 제시.</t>
+          <t>정치적 발언 및 특정 지역 반도체 관련 사업에 대한 비판적인 의견이 지배적이다. 정부 정책 및 정치적 이슈와 관련된 부정적인 전망이 주를 이룬다.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['공매도', '외인 매도', '목표가']</t>
+          <t>['정부 정책', '지역 이슈', '정치적 발언']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_13.xlsx
+++ b/data/trending_integrated_20261013_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F2" t="n">
         <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87579099850</v>
+        <v>87605966650</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17440</v>
+        <v>12120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.67%</t>
+          <t>'+9.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E3" t="n">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
-        <v>158</v>
+        <v>443</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K3" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L3" t="n">
-        <v>19930</v>
+        <v>13970</v>
       </c>
       <c r="M3" t="n">
-        <v>15520</v>
+        <v>10810</v>
       </c>
       <c r="N3" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O3" t="n">
-        <v>238227112600</v>
+        <v>356451901875</v>
       </c>
       <c r="P3" t="n">
-        <v>19930</v>
+        <v>14350</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-203000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 기술의 중요성과 함께 주가 상승에 대한 기대가 나타난다. 미국 보안주 폭락 및 글로벌 경기 침체 우려도 언급된다.</t>
+          <t>단기 급등 후 변동성 확대, 일부 투자자 이탈 관측. 주포의 움직임 및 향후 주가 흐름에 대한 다양한 의견 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안 기술', '주가 상승', '경기 침체']</t>
+          <t>['주포', '변동성', '매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11740</v>
+        <v>17350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.05%</t>
+          <t>'+6.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>425</v>
+        <v>159</v>
       </c>
       <c r="H4" t="n">
-        <v>15.64</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11070</v>
+        <v>16350</v>
       </c>
       <c r="K4" t="n">
-        <v>11670</v>
+        <v>15790</v>
       </c>
       <c r="L4" t="n">
-        <v>13970</v>
+        <v>19930</v>
       </c>
       <c r="M4" t="n">
-        <v>10810</v>
+        <v>15520</v>
       </c>
       <c r="N4" t="n">
-        <v>14.72</v>
+        <v>1.13</v>
       </c>
       <c r="O4" t="n">
-        <v>346296767705</v>
+        <v>241347416260</v>
       </c>
       <c r="P4" t="n">
-        <v>14350</v>
+        <v>19930</v>
       </c>
       <c r="Q4" t="n">
-        <v>465</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-176000</v>
+        <v>30000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>개인 투자자들의 매도와 매수에 대한 엇갈린 의견이 존재하며, 일부는 주포의 움직임을 주시하고 있다. 테마의 영향력 약화 및 주가 변동성에 대한 언급이 있다.</t>
+          <t>보안주 전반의 흐름 속에서 기술력에 대한 기대감 표출. 신고가 경신 및 10% 이상 상승 가능성 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '테마', '물갈이']</t>
+          <t>['보안', '기술', '신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3725</v>
+        <v>3805</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+2.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H5" t="n">
         <v>0.91</v>
@@ -886,7 +886,7 @@
         <v>0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>87993113069</v>
+        <v>88888914442</v>
       </c>
       <c r="P5" t="n">
         <v>6660</v>
@@ -895,10 +895,10 @@
         <v>2200</v>
       </c>
       <c r="R5" t="n">
-        <v>-34000</v>
+        <v>-120000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1565</v>
+        <v>1577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H6" t="n">
         <v>0.32</v>
@@ -978,7 +978,7 @@
         <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>8998939078</v>
+        <v>9051938847</v>
       </c>
       <c r="P6" t="n">
         <v>2930</v>
@@ -987,7 +987,7 @@
         <v>910</v>
       </c>
       <c r="R6" t="n">
-        <v>34000</v>
+        <v>53000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13170</v>
+        <v>43650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-0.23</v>
       </c>
       <c r="E7" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="G7" t="n">
-        <v>248</v>
+        <v>703</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>13.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13410</v>
+        <v>44400</v>
       </c>
       <c r="K7" t="n">
-        <v>13260</v>
+        <v>43300</v>
       </c>
       <c r="L7" t="n">
-        <v>14580</v>
+        <v>44100</v>
       </c>
       <c r="M7" t="n">
-        <v>12920</v>
+        <v>42250</v>
       </c>
       <c r="N7" t="n">
-        <v>0.21</v>
+        <v>13.33</v>
       </c>
       <c r="O7" t="n">
-        <v>63208617305</v>
+        <v>25661737225</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>34000</v>
+        <v>70000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 좌절감과 함께 매수세 대비 매도세 우위, 종가 하락 예상 등 부정적 전망.</t>
+          <t>신약 승인 및 임상 결과에 대한 기대감이 존재하며, 공매도 세력에 대한 언급이 있다. 주가 상승 가능성과 악재 반영 여부에 대한 논의가 진행 중이다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['매도세', '주가 하락', '종가']</t>
+          <t>['신약 승인', '공매도', '임상 결과']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43550</v>
+        <v>17640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'-2.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.23</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>692</v>
+        <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>13.1</v>
+        <v>27.69</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>44400</v>
+        <v>18010</v>
       </c>
       <c r="K8" t="n">
-        <v>43300</v>
+        <v>17430</v>
       </c>
       <c r="L8" t="n">
-        <v>44100</v>
+        <v>17840</v>
       </c>
       <c r="M8" t="n">
-        <v>42250</v>
+        <v>17210</v>
       </c>
       <c r="N8" t="n">
-        <v>13.33</v>
+        <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>25269078975</v>
+        <v>54875288685</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>45000</v>
+        <v>743000</v>
       </c>
       <c r="S8" t="n">
-        <v>7000</v>
+        <v>65000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>신약 승인 및 임상 결과에 대한 기대감이 존재하며, 공매도 세력에 대한 언급이 있다. 주가 상승 가능성과 악재 반영 여부에 대한 논의가 진행 중이다.</t>
+          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['신약 승인', '공매도', '임상 결과']</t>
+          <t>['FLNG', '매출 전망', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,130 +1200,130 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17650</v>
+        <v>6060</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>297</v>
+        <v>124</v>
       </c>
       <c r="H9" t="n">
-        <v>27.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18010</v>
+        <v>6210</v>
       </c>
       <c r="K9" t="n">
-        <v>17430</v>
+        <v>5950</v>
       </c>
       <c r="L9" t="n">
-        <v>17840</v>
+        <v>6560</v>
       </c>
       <c r="M9" t="n">
-        <v>17210</v>
+        <v>5840</v>
       </c>
       <c r="N9" t="n">
-        <v>27.61</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>53699335045</v>
+        <v>23020846855</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>11370</v>
       </c>
       <c r="Q9" t="n">
-        <v>17210</v>
+        <v>3300</v>
       </c>
       <c r="R9" t="n">
-        <v>681000</v>
+        <v>78000</v>
       </c>
       <c r="S9" t="n">
-        <v>71000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '목표가']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18110</v>
+        <v>13080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.37%</t>
+          <t>'-2.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>88</v>
+        <v>261</v>
       </c>
       <c r="H10" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18550</v>
+        <v>13410</v>
       </c>
       <c r="K10" t="n">
-        <v>17550</v>
+        <v>13260</v>
       </c>
       <c r="L10" t="n">
-        <v>19580</v>
+        <v>14580</v>
       </c>
       <c r="M10" t="n">
-        <v>17010</v>
+        <v>12920</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="O10" t="n">
-        <v>71584210210</v>
+        <v>63784698270</v>
       </c>
       <c r="P10" t="n">
-        <v>30550</v>
+        <v>28700</v>
       </c>
       <c r="Q10" t="n">
-        <v>6100</v>
+        <v>11600</v>
       </c>
       <c r="R10" t="n">
-        <v>-65000</v>
+        <v>31000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내 해킹 이슈 및 보안주 강세 흐름 속에서 엑스게이트 주가 급등 기대감 표출. 매집 의혹 및 추가 상승 전망.</t>
+          <t>주가 하락에 대한 좌절감과 함께 매수세 대비 매도세 우위, 종가 하락 예상 등 부정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '급등']</t>
+          <t>['매도세', '주가 하락', '종가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15660</v>
+        <v>18090</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.16</v>
+        <v>-0.42</v>
       </c>
       <c r="E11" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>377</v>
+        <v>88</v>
       </c>
       <c r="H11" t="n">
-        <v>9.630000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16090</v>
+        <v>18550</v>
       </c>
       <c r="K11" t="n">
-        <v>15190</v>
+        <v>17550</v>
       </c>
       <c r="L11" t="n">
-        <v>15980</v>
+        <v>19580</v>
       </c>
       <c r="M11" t="n">
-        <v>15100</v>
+        <v>17010</v>
       </c>
       <c r="N11" t="n">
-        <v>9.470000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="O11" t="n">
-        <v>50636799200</v>
+        <v>71830749375</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R11" t="n">
-        <v>395000</v>
+        <v>-36000</v>
       </c>
       <c r="S11" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 우려와 함께 공매도 및 대차해지에 대한 논의가 있다. 건설주 전반의 부진과 국내 증시 상황에 대한 부정적인 인식이 나타난다.</t>
+          <t>국내 해킹 이슈 및 보안주 강세 흐름 속에서 엑스게이트 주가 급등 기대감 표출. 매집 의혹 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '증시 상황']</t>
+          <t>['해킹', '보안주', '급등']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,99 +1476,99 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6030</v>
+        <v>15630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E12" t="n">
+        <v>147</v>
+      </c>
+      <c r="F12" t="n">
         <v>63</v>
       </c>
-      <c r="F12" t="n">
-        <v>23</v>
-      </c>
       <c r="G12" t="n">
-        <v>124</v>
+        <v>376</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6210</v>
+        <v>16090</v>
       </c>
       <c r="K12" t="n">
-        <v>5950</v>
+        <v>15190</v>
       </c>
       <c r="L12" t="n">
-        <v>6560</v>
+        <v>15980</v>
       </c>
       <c r="M12" t="n">
-        <v>5840</v>
+        <v>15100</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>22958570035</v>
+        <v>51503724565</v>
       </c>
       <c r="P12" t="n">
-        <v>11370</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-5000</v>
+        <v>630000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>금감원 사모펀드 점검 관련 언급. 주가 하락에 대한 우려와 함께 공매도 및 대차 해지 관련 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['금감원', '공매도', '사모펀드']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69200</v>
+        <v>69100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-3.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F13" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G13" t="n">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="H13" t="n">
         <v>22.1</v>
@@ -1622,7 +1622,7 @@
         <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>140460293350</v>
+        <v>146585397950</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1631,10 +1631,10 @@
         <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>225000</v>
+        <v>85000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-50000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7450</v>
+        <v>19750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.99%</t>
+          <t>'-3.42%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>0.39</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>267</v>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="G14" t="n">
-        <v>427</v>
+        <v>370</v>
       </c>
       <c r="H14" t="n">
-        <v>26.01</v>
+        <v>0.73</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7760</v>
+        <v>20450</v>
       </c>
       <c r="K14" t="n">
-        <v>7650</v>
+        <v>19540</v>
       </c>
       <c r="L14" t="n">
-        <v>7680</v>
+        <v>23100</v>
       </c>
       <c r="M14" t="n">
-        <v>7300</v>
+        <v>17540</v>
       </c>
       <c r="N14" t="n">
-        <v>26.37</v>
+        <v>0.34</v>
       </c>
       <c r="O14" t="n">
-        <v>22080822745</v>
+        <v>82856285270</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>62100</v>
       </c>
       <c r="Q14" t="n">
-        <v>7300</v>
+        <v>17540</v>
       </c>
       <c r="R14" t="n">
-        <v>-510000</v>
+        <v>-3000</v>
       </c>
       <c r="S14" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 지속 및 회사 실적 부진에 대한 우려 제기. 상폐 또는 매각 관련 언급과 함께 일부 긍정적 전망 혼재.</t>
+          <t>주가 조작 및 물량 떠넘기기 의혹 제기. 자체 로봇 제작 기술 부족 지적. 정치적 이슈와 연계된 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가하락', '실적', '상폐']</t>
+          <t>['주가 조작', '로봇', '기술']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6490</v>
+        <v>7430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.25%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>609</v>
+        <v>425</v>
       </c>
       <c r="H15" t="n">
-        <v>12.27</v>
+        <v>26.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6810</v>
+        <v>7760</v>
       </c>
       <c r="K15" t="n">
-        <v>7150</v>
+        <v>7650</v>
       </c>
       <c r="L15" t="n">
-        <v>7160</v>
+        <v>7680</v>
       </c>
       <c r="M15" t="n">
-        <v>6440</v>
+        <v>7300</v>
       </c>
       <c r="N15" t="n">
-        <v>12.57</v>
+        <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>19786520525</v>
+        <v>22508434135</v>
       </c>
       <c r="P15" t="n">
-        <v>8850</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>4220</v>
+        <v>7300</v>
       </c>
       <c r="R15" t="n">
-        <v>-606000</v>
+        <v>-822000</v>
       </c>
       <c r="S15" t="n">
-        <v>-8000</v>
+        <v>24000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기 및 공매도 언급, 작년 실적 기반 주가 상승 기대. 금호타이어 부지 실체 언급.</t>
+          <t>주가 하락 지속 및 회사 실적 부진에 대한 우려 제기. 상폐 또는 매각 관련 언급과 함께 일부 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '주가 상승']</t>
+          <t>['주가하락', '실적', '상폐']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14640</v>
+        <v>6490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.87%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>380</v>
+        <v>630</v>
       </c>
       <c r="H16" t="n">
-        <v>3.43</v>
+        <v>12.27</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>15720</v>
+        <v>6810</v>
       </c>
       <c r="K16" t="n">
-        <v>14770</v>
+        <v>7150</v>
       </c>
       <c r="L16" t="n">
-        <v>15130</v>
+        <v>7160</v>
       </c>
       <c r="M16" t="n">
-        <v>14160</v>
+        <v>6440</v>
       </c>
       <c r="N16" t="n">
-        <v>3.37</v>
+        <v>12.57</v>
       </c>
       <c r="O16" t="n">
-        <v>74756849400</v>
+        <v>19961068275</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>8850</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>4220</v>
       </c>
       <c r="R16" t="n">
-        <v>85000</v>
+        <v>-514000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>-1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
+          <t>의도적 주가 누르기 및 공매도 관련 비판. 긍정적 실적 대비 주가 부진에 대한 불만 표출. 송정역 부지 관련 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '외인매수', '공장']</t>
+          <t>['공매도', '실적', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6880</v>
+        <v>12510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.15%</t>
+          <t>'-6.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.19</v>
+        <v>-1.01</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7410</v>
+        <v>13400</v>
       </c>
       <c r="K17" t="n">
-        <v>7330</v>
+        <v>13750</v>
       </c>
       <c r="L17" t="n">
-        <v>8040</v>
+        <v>15390</v>
       </c>
       <c r="M17" t="n">
-        <v>6810</v>
+        <v>11980</v>
       </c>
       <c r="N17" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="O17" t="n">
-        <v>65380850220</v>
+        <v>190284456680</v>
       </c>
       <c r="P17" t="n">
-        <v>23500</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>2890</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-241000</v>
+        <v>4000</v>
       </c>
       <c r="S17" t="n">
-        <v>-130000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>건설기초소재대장주로 언급되며 수도권 거점 공장 보유. 일부 투자자는 차익 실현 매도를 하였으나, 바닥 지지 및 매집 정황을 근거로 매수 진입을 고려하는 의견도 있음.</t>
+          <t>주가 상승에 대한 기대와 공매도에 대한 우려가 혼재되어 있으며, 일부 투자자는 목표가를 제시하고 있다. 최근 주가 흐름에 대한 부정적인 인식이 있다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['건설기초소재', '거점공장', '매집']</t>
+          <t>['공매도', '목표가', '주가 흐름']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12440</v>
+        <v>172900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.16%</t>
+          <t>'-7.44%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>366</v>
+        <v>127</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,235 +2067,235 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13400</v>
+        <v>186800</v>
       </c>
       <c r="K18" t="n">
-        <v>13750</v>
+        <v>180800</v>
       </c>
       <c r="L18" t="n">
-        <v>15390</v>
+        <v>183000</v>
       </c>
       <c r="M18" t="n">
-        <v>11980</v>
+        <v>170000</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>75.23</v>
       </c>
       <c r="O18" t="n">
-        <v>187819858250</v>
+        <v>582153824400</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>70400</v>
       </c>
       <c r="R18" t="n">
-        <v>-76000</v>
+        <v>-532000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>92000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대와 공매도에 대한 우려가 혼재되어 있으며, 일부 투자자는 목표가를 제시하고 있다. 최근 주가 흐름에 대한 부정적인 인식이 있다.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '목표가', '주가 흐름']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>172800</v>
+        <v>14520</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.49%</t>
+          <t>'-7.63%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
+        <v>113</v>
+      </c>
+      <c r="F19" t="n">
         <v>74</v>
       </c>
-      <c r="F19" t="n">
-        <v>53</v>
-      </c>
       <c r="G19" t="n">
-        <v>127</v>
+        <v>384</v>
       </c>
       <c r="H19" t="n">
-        <v>75.20999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>186800</v>
+        <v>15720</v>
       </c>
       <c r="K19" t="n">
-        <v>180800</v>
+        <v>14770</v>
       </c>
       <c r="L19" t="n">
-        <v>183000</v>
+        <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>170000</v>
+        <v>14160</v>
       </c>
       <c r="N19" t="n">
-        <v>75.23</v>
+        <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>570766249300</v>
+        <v>75848219010</v>
       </c>
       <c r="P19" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>70400</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-173000</v>
+        <v>79000</v>
       </c>
       <c r="S19" t="n">
-        <v>65000</v>
+        <v>-7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['어닝서프라이즈', '외인매수', '공장']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>231000</v>
+        <v>6830</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-7.83%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F20" t="n">
-        <v>574</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>1769</v>
+        <v>331</v>
       </c>
       <c r="H20" t="n">
-        <v>46.3</v>
+        <v>1.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>250500</v>
+        <v>7410</v>
       </c>
       <c r="K20" t="n">
-        <v>241500</v>
+        <v>7330</v>
       </c>
       <c r="L20" t="n">
-        <v>244000</v>
+        <v>8040</v>
       </c>
       <c r="M20" t="n">
-        <v>228000</v>
+        <v>6810</v>
       </c>
       <c r="N20" t="n">
-        <v>46.35</v>
+        <v>1.99</v>
       </c>
       <c r="O20" t="n">
-        <v>3638738664250</v>
+        <v>65609584800</v>
       </c>
       <c r="P20" t="n">
-        <v>374500</v>
+        <v>23500</v>
       </c>
       <c r="Q20" t="n">
-        <v>90200</v>
+        <v>2890</v>
       </c>
       <c r="R20" t="n">
-        <v>-2204000</v>
+        <v>-286000</v>
       </c>
       <c r="S20" t="n">
-        <v>241000</v>
+        <v>-184000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 발언 및 특정 지역에 대한 부정적인 의견이 주를 이루며, 정부 정책 및 리더십에 대한 비판이 제기되고 있다. 반도체 공장 설립 관련 논란도 언급된다.</t>
+          <t>성수 메가프로젝트 및 건설기초소재 관련 언급. 주가 부진 및 대차 물량 증가에 대한 우려 제기. 바닥 지지 확인 후 진입 의견.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정부 정책', '반도체', '지역갈등']</t>
+          <t>['건설', '소재', '대차']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,26 +2304,26 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1457000</v>
+        <v>230750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-9.22%</t>
+          <t>'-7.88%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E21" t="n">
         <v>800</v>
@@ -2332,10 +2332,10 @@
         <v>569</v>
       </c>
       <c r="G21" t="n">
-        <v>1891</v>
+        <v>1847</v>
       </c>
       <c r="H21" t="n">
-        <v>49.41</v>
+        <v>46.3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1605000</v>
+        <v>250500</v>
       </c>
       <c r="K21" t="n">
-        <v>1538000</v>
+        <v>241500</v>
       </c>
       <c r="L21" t="n">
-        <v>1554000</v>
+        <v>244000</v>
       </c>
       <c r="M21" t="n">
-        <v>1445000</v>
+        <v>228000</v>
       </c>
       <c r="N21" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4810698052500</v>
+        <v>3707996617000</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q21" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R21" t="n">
-        <v>-722000</v>
+        <v>-4524000</v>
       </c>
       <c r="S21" t="n">
-        <v>88000</v>
+        <v>383000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>정치적 발언 및 특정 지역 반도체 관련 사업에 대한 비판적인 의견이 지배적이다. 정부 정책 및 정치적 이슈와 관련된 부정적인 전망이 주를 이룬다.</t>
+          <t>정치적 발언 및 특정 지역 투자 반대 의견 표출. 반도체 산업 및 국가 경제에 대한 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['정부 정책', '지역 이슈', '정치적 발언']</t>
+          <t>['정치', '반도체', '경제']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2395,6 +2395,98 @@
         </is>
       </c>
       <c r="Z21" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1447000</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-9.84%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E22" t="n">
+        <v>800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>574</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1941</v>
+      </c>
+      <c r="H22" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1445000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4956494409500</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-1103000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>137000</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 연계된 부정적 여론 형성. 반도체 공장 건설 및 정부 정책에 대한 비판적 시각.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['반도체', '정치', '공장']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261013_13.xlsx
+++ b/data/trending_integrated_20261013_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87605966650</v>
+        <v>87625142170</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12120</v>
+        <v>4640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.49%</t>
+          <t>'+19.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>443</v>
+        <v>135</v>
       </c>
       <c r="H3" t="n">
-        <v>15.64</v>
+        <v>2.05</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11070</v>
+        <v>3895</v>
       </c>
       <c r="K3" t="n">
-        <v>11670</v>
+        <v>3730</v>
       </c>
       <c r="L3" t="n">
-        <v>13970</v>
+        <v>4770</v>
       </c>
       <c r="M3" t="n">
-        <v>10810</v>
+        <v>3650</v>
       </c>
       <c r="N3" t="n">
-        <v>14.72</v>
+        <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>356451901875</v>
+        <v>82722896950</v>
       </c>
       <c r="P3" t="n">
-        <v>14350</v>
+        <v>5470</v>
       </c>
       <c r="Q3" t="n">
-        <v>465</v>
+        <v>2810</v>
       </c>
       <c r="R3" t="n">
-        <v>-203000</v>
+        <v>-96000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>단기 급등 후 변동성 확대, 일부 투자자 이탈 관측. 주포의 움직임 및 향후 주가 흐름에 대한 다양한 의견 존재.</t>
+          <t>러시아 흑사병 테마 관련 국제약품의 치료제 부각. 신풍제약 과거 사례 비교 및 텐버거 기대. 경영권 승계 이슈도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주포', '변동성', '매도']</t>
+          <t>['흑사병 테마', '치료제', '경영권 승계']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17350</v>
+        <v>11830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.12%</t>
+          <t>'+6.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>159</v>
+        <v>442</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K4" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L4" t="n">
-        <v>19930</v>
+        <v>13970</v>
       </c>
       <c r="M4" t="n">
-        <v>15520</v>
+        <v>10810</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>241347416260</v>
+        <v>363601314490</v>
       </c>
       <c r="P4" t="n">
-        <v>19930</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>30000</v>
+        <v>-203000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>보안주 전반의 흐름 속에서 기술력에 대한 기대감 표출. 신고가 경신 및 10% 이상 상승 가능성 전망.</t>
+          <t>주포의 의도적인 흔들기와 물량 소화 후 급등 전망. 호남클러스터 외 테마 소멸. 종가 5% 부근 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안', '기술', '신고가']</t>
+          <t>['주포', '물량 소화', '급등 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3805</v>
+        <v>17360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.56%</t>
+          <t>'+6.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3710</v>
+        <v>16350</v>
       </c>
       <c r="K5" t="n">
-        <v>3555</v>
+        <v>15790</v>
       </c>
       <c r="L5" t="n">
-        <v>4440</v>
+        <v>19930</v>
       </c>
       <c r="M5" t="n">
-        <v>3475</v>
+        <v>15520</v>
       </c>
       <c r="N5" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>88888914442</v>
+        <v>242183071815</v>
       </c>
       <c r="P5" t="n">
-        <v>6660</v>
+        <v>19930</v>
       </c>
       <c r="Q5" t="n">
-        <v>2200</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-120000</v>
+        <v>30000</v>
       </c>
       <c r="S5" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신규 질병 발생 가능성에 대한 언급과 함께 주가 상승에 대한 기대가 존재한다. 페스트, 독감 등 질병 관련 뉴스가 주가 변동의 주요 요인으로 작용하고 있다.</t>
+          <t>보안주 전반의 흐름 속에서 기술력에 대한 기대감 표출. 신고가 경신 및 10% 이상 상승 가능성 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['질병', '주가 상승', '뉴스']</t>
+          <t>['보안', '기술', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1577</v>
+        <v>3930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+5.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1578</v>
+        <v>3710</v>
       </c>
       <c r="K6" t="n">
-        <v>1578</v>
+        <v>3555</v>
       </c>
       <c r="L6" t="n">
-        <v>1776</v>
+        <v>4440</v>
       </c>
       <c r="M6" t="n">
-        <v>1457</v>
+        <v>3475</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>9051938847</v>
+        <v>90990277863</v>
       </c>
       <c r="P6" t="n">
-        <v>2930</v>
+        <v>6660</v>
       </c>
       <c r="Q6" t="n">
-        <v>910</v>
+        <v>2200</v>
       </c>
       <c r="R6" t="n">
-        <v>53000</v>
+        <v>-120000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>경제자유구역 추가 편입 및 메가프로젝트 투자에 대한 긍정적인 전망이 있다. 주가 상승에 대한 기대감과 함께 일부 투자자 간의 의견 대립이 관찰된다.</t>
+          <t>신규 질병 발생 가능성에 대한 언급과 함께 주가 상승에 대한 기대가 존재한다. 페스트, 독감 등 질병 관련 뉴스가 주가 변동의 주요 요인으로 작용하고 있다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경제자유구역', '투자', '주가 상승']</t>
+          <t>['질병', '주가 상승', '뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43650</v>
+        <v>1560</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>703</v>
+        <v>230</v>
       </c>
       <c r="H7" t="n">
-        <v>13.1</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>44400</v>
+        <v>1578</v>
       </c>
       <c r="K7" t="n">
-        <v>43300</v>
+        <v>1578</v>
       </c>
       <c r="L7" t="n">
-        <v>44100</v>
+        <v>1776</v>
       </c>
       <c r="M7" t="n">
-        <v>42250</v>
+        <v>1457</v>
       </c>
       <c r="N7" t="n">
-        <v>13.33</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>25661737225</v>
+        <v>9106903711</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>2930</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>910</v>
       </c>
       <c r="R7" t="n">
-        <v>70000</v>
+        <v>53000</v>
       </c>
       <c r="S7" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 승인 및 임상 결과에 대한 기대감이 존재하며, 공매도 세력에 대한 언급이 있다. 주가 상승 가능성과 악재 반영 여부에 대한 논의가 진행 중이다.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약 승인', '공매도', '임상 결과']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17640</v>
+        <v>17660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.05%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H8" t="n">
         <v>27.69</v>
@@ -1162,7 +1162,7 @@
         <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>54875288685</v>
+        <v>56407729095</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 뉴스 인용 및 목표가 42,000원 언급, 주주 환원 정책 요구 및 현 주가 불만 표출.</t>
+          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '목표가']</t>
+          <t>['FLNG', '매출 확대', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6060</v>
+        <v>43450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G9" t="n">
-        <v>124</v>
+        <v>710</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6210</v>
+        <v>44400</v>
       </c>
       <c r="K9" t="n">
-        <v>5950</v>
+        <v>43300</v>
       </c>
       <c r="L9" t="n">
-        <v>6560</v>
+        <v>44100</v>
       </c>
       <c r="M9" t="n">
-        <v>5840</v>
+        <v>42250</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>23020846855</v>
+        <v>26152286725</v>
       </c>
       <c r="P9" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>78000</v>
+        <v>70000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 기대감 및 C1 확정 가능성 제기. 공매도 세력의 움직임과 악성 매물대 소화 필요성 언급. 통합 IR 데이 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['리보', '캄렐', '간암 1차 승인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13080</v>
+        <v>13100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.46%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" t="n">
         <v>261</v>
@@ -1346,7 +1346,7 @@
         <v>0.21</v>
       </c>
       <c r="O10" t="n">
-        <v>63784698270</v>
+        <v>64034203065</v>
       </c>
       <c r="P10" t="n">
         <v>28700</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18090</v>
+        <v>19970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.35%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.42</v>
+        <v>0.39</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>274</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="G11" t="n">
-        <v>88</v>
+        <v>383</v>
       </c>
       <c r="H11" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18550</v>
+        <v>20450</v>
       </c>
       <c r="K11" t="n">
-        <v>17550</v>
+        <v>19540</v>
       </c>
       <c r="L11" t="n">
-        <v>19580</v>
+        <v>23100</v>
       </c>
       <c r="M11" t="n">
-        <v>17010</v>
+        <v>17540</v>
       </c>
       <c r="N11" t="n">
-        <v>0.88</v>
+        <v>0.34</v>
       </c>
       <c r="O11" t="n">
-        <v>71830749375</v>
+        <v>83952194095</v>
       </c>
       <c r="P11" t="n">
-        <v>30550</v>
+        <v>62100</v>
       </c>
       <c r="Q11" t="n">
-        <v>6100</v>
+        <v>17540</v>
       </c>
       <c r="R11" t="n">
-        <v>-36000</v>
+        <v>-3000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 해킹 이슈 및 보안주 강세 흐름 속에서 엑스게이트 주가 급등 기대감 표출. 매집 의혹 및 추가 상승 전망.</t>
+          <t>주가 조작 및 물량 떠넘기기 의혹 제기. 자체 로봇 제작 기술 부족 지적. 정치적 이슈와 연계된 부정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '급등']</t>
+          <t>['주가 조작', '로봇', '기술']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15630</v>
+        <v>18060</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-2.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.16</v>
+        <v>-0.42</v>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>376</v>
+        <v>89</v>
       </c>
       <c r="H12" t="n">
-        <v>9.630000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16090</v>
+        <v>18550</v>
       </c>
       <c r="K12" t="n">
-        <v>15190</v>
+        <v>17550</v>
       </c>
       <c r="L12" t="n">
-        <v>15980</v>
+        <v>19580</v>
       </c>
       <c r="M12" t="n">
-        <v>15100</v>
+        <v>17010</v>
       </c>
       <c r="N12" t="n">
-        <v>9.470000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="O12" t="n">
-        <v>51503724565</v>
+        <v>72195017040</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R12" t="n">
-        <v>630000</v>
+        <v>-36000</v>
       </c>
       <c r="S12" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금감원 사모펀드 점검 관련 언급. 주가 하락에 대한 우려와 함께 공매도 및 대차 해지 관련 논의.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['금감원', '공매도', '사모펀드']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69100</v>
+        <v>15640</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E13" t="n">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>740</v>
+        <v>381</v>
       </c>
       <c r="H13" t="n">
-        <v>22.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>71500</v>
+        <v>16090</v>
       </c>
       <c r="K13" t="n">
-        <v>68400</v>
+        <v>15190</v>
       </c>
       <c r="L13" t="n">
-        <v>70600</v>
+        <v>15980</v>
       </c>
       <c r="M13" t="n">
-        <v>67300</v>
+        <v>15100</v>
       </c>
       <c r="N13" t="n">
-        <v>22.21</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>146585397950</v>
+        <v>52644492955</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>85000</v>
+        <v>630000</v>
       </c>
       <c r="S13" t="n">
-        <v>-50000</v>
+        <v>48000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 부양 실패 및 도박판 비유, 특정 정치인 비난과 함께 반대매매 및 주가 하락 가능성 언급.</t>
+          <t>금감원 사모펀드 점검 관련 언급. 주가 하락에 대한 우려와 함께 공매도 및 대차 해지 관련 논의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['도박판', '반대매매', '주가 하락']</t>
+          <t>['금감원', '공매도', '사모펀드']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19750</v>
+        <v>6030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.39</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>370</v>
+        <v>124</v>
       </c>
       <c r="H14" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>20450</v>
+        <v>6210</v>
       </c>
       <c r="K14" t="n">
-        <v>19540</v>
+        <v>5950</v>
       </c>
       <c r="L14" t="n">
-        <v>23100</v>
+        <v>6560</v>
       </c>
       <c r="M14" t="n">
-        <v>17540</v>
+        <v>5840</v>
       </c>
       <c r="N14" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="O14" t="n">
-        <v>82856285270</v>
+        <v>23081750505</v>
       </c>
       <c r="P14" t="n">
-        <v>62100</v>
+        <v>11370</v>
       </c>
       <c r="Q14" t="n">
-        <v>17540</v>
+        <v>3300</v>
       </c>
       <c r="R14" t="n">
-        <v>-3000</v>
+        <v>78000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 물량 떠넘기기 의혹 제기. 자체 로봇 제작 기술 부족 지적. 정치적 이슈와 연계된 부정적 전망.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '로봇', '기술']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,43 +1747,43 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7430</v>
+        <v>69200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.25%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.36</v>
+        <v>-0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="G15" t="n">
-        <v>425</v>
+        <v>744</v>
       </c>
       <c r="H15" t="n">
-        <v>26.01</v>
+        <v>22.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7760</v>
+        <v>71500</v>
       </c>
       <c r="K15" t="n">
-        <v>7650</v>
+        <v>68400</v>
       </c>
       <c r="L15" t="n">
-        <v>7680</v>
+        <v>70600</v>
       </c>
       <c r="M15" t="n">
-        <v>7300</v>
+        <v>67300</v>
       </c>
       <c r="N15" t="n">
-        <v>26.37</v>
+        <v>22.21</v>
       </c>
       <c r="O15" t="n">
-        <v>22508434135</v>
+        <v>149636812850</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>7300</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-822000</v>
+        <v>85000</v>
       </c>
       <c r="S15" t="n">
-        <v>24000</v>
+        <v>-50000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 지속 및 회사 실적 부진에 대한 우려 제기. 상폐 또는 매각 관련 언급과 함께 일부 긍정적 전망 혼재.</t>
+          <t>주가 부양 실패 및 도박판 비유, 특정 정치인 비난과 함께 반대매매 및 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가하락', '실적', '상폐']</t>
+          <t>['도박판', '반대매매', '주가 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6490</v>
+        <v>7440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.12%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>630</v>
+        <v>422</v>
       </c>
       <c r="H16" t="n">
-        <v>12.27</v>
+        <v>26.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6810</v>
+        <v>7760</v>
       </c>
       <c r="K16" t="n">
-        <v>7150</v>
+        <v>7650</v>
       </c>
       <c r="L16" t="n">
-        <v>7160</v>
+        <v>7680</v>
       </c>
       <c r="M16" t="n">
-        <v>6440</v>
+        <v>7300</v>
       </c>
       <c r="N16" t="n">
-        <v>12.57</v>
+        <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>19961068275</v>
+        <v>22936866055</v>
       </c>
       <c r="P16" t="n">
-        <v>8850</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>4220</v>
+        <v>7300</v>
       </c>
       <c r="R16" t="n">
-        <v>-514000</v>
+        <v>-822000</v>
       </c>
       <c r="S16" t="n">
-        <v>-1000</v>
+        <v>24000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>의도적 주가 누르기 및 공매도 관련 비판. 긍정적 실적 대비 주가 부진에 대한 불만 표출. 송정역 부지 관련 언급.</t>
+          <t>주가 하락 지속 및 회사 실적 부진에 대한 우려 제기. 상폐 또는 매각 관련 언급과 함께 일부 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '주가']</t>
+          <t>['주가하락', '실적', '상폐']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12510</v>
+        <v>6490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.64%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.01</v>
+        <v>-0.3</v>
       </c>
       <c r="E17" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>371</v>
+        <v>631</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>12.27</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13400</v>
+        <v>6810</v>
       </c>
       <c r="K17" t="n">
-        <v>13750</v>
+        <v>7150</v>
       </c>
       <c r="L17" t="n">
-        <v>15390</v>
+        <v>7160</v>
       </c>
       <c r="M17" t="n">
-        <v>11980</v>
+        <v>6440</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>12.57</v>
       </c>
       <c r="O17" t="n">
-        <v>190284456680</v>
+        <v>20133592870</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>8850</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>4220</v>
       </c>
       <c r="R17" t="n">
-        <v>4000</v>
+        <v>-514000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대와 공매도에 대한 우려가 혼재되어 있으며, 일부 투자자는 목표가를 제시하고 있다. 최근 주가 흐름에 대한 부정적인 인식이 있다.</t>
+          <t>의도적 주가 누르기 및 공매도 관련 비판. 긍정적 실적 대비 주가 부진에 대한 불만 표출. 송정역 부지 관련 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '목표가', '주가 흐름']</t>
+          <t>['공매도', '실적', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,191 +2028,191 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>172900</v>
+        <v>14510</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.44%</t>
+          <t>'-7.70%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
+        <v>113</v>
+      </c>
+      <c r="F18" t="n">
         <v>74</v>
       </c>
-      <c r="F18" t="n">
-        <v>53</v>
-      </c>
       <c r="G18" t="n">
-        <v>127</v>
+        <v>391</v>
       </c>
       <c r="H18" t="n">
-        <v>75.20999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>186800</v>
+        <v>15720</v>
       </c>
       <c r="K18" t="n">
-        <v>180800</v>
+        <v>14770</v>
       </c>
       <c r="L18" t="n">
-        <v>183000</v>
+        <v>15130</v>
       </c>
       <c r="M18" t="n">
-        <v>170000</v>
+        <v>14160</v>
       </c>
       <c r="N18" t="n">
-        <v>75.23</v>
+        <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>582153824400</v>
+        <v>76928289340</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>70400</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-532000</v>
+        <v>79000</v>
       </c>
       <c r="S18" t="n">
-        <v>92000</v>
+        <v>-7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['어닝서프라이즈', '외인매수', '공장']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14520</v>
+        <v>172300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.63%</t>
+          <t>'-7.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="H19" t="n">
-        <v>3.43</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15720</v>
+        <v>186800</v>
       </c>
       <c r="K19" t="n">
-        <v>14770</v>
+        <v>180800</v>
       </c>
       <c r="L19" t="n">
-        <v>15130</v>
+        <v>183000</v>
       </c>
       <c r="M19" t="n">
-        <v>14160</v>
+        <v>170000</v>
       </c>
       <c r="N19" t="n">
-        <v>3.37</v>
+        <v>75.23</v>
       </c>
       <c r="O19" t="n">
-        <v>75848219010</v>
+        <v>594547688500</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>243500</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>70400</v>
       </c>
       <c r="R19" t="n">
-        <v>79000</v>
+        <v>-532000</v>
       </c>
       <c r="S19" t="n">
-        <v>-7000</v>
+        <v>92000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '외인매수', '공장']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6830</v>
+        <v>6820</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.83%</t>
+          <t>'-7.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.19</v>
       </c>
       <c r="E20" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H20" t="n">
         <v>1.8</v>
@@ -2266,7 +2266,7 @@
         <v>1.99</v>
       </c>
       <c r="O20" t="n">
-        <v>65609584800</v>
+        <v>65981332350</v>
       </c>
       <c r="P20" t="n">
         <v>23500</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>230750</v>
+        <v>12330</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'-7.99%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>-1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>165</v>
       </c>
       <c r="F21" t="n">
-        <v>569</v>
+        <v>95</v>
       </c>
       <c r="G21" t="n">
-        <v>1847</v>
+        <v>392</v>
       </c>
       <c r="H21" t="n">
-        <v>46.3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>250500</v>
+        <v>13400</v>
       </c>
       <c r="K21" t="n">
-        <v>241500</v>
+        <v>13750</v>
       </c>
       <c r="L21" t="n">
-        <v>244000</v>
+        <v>15390</v>
       </c>
       <c r="M21" t="n">
-        <v>228000</v>
+        <v>11980</v>
       </c>
       <c r="N21" t="n">
-        <v>46.35</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>3707996617000</v>
+        <v>191661610185</v>
       </c>
       <c r="P21" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>90200</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-4524000</v>
+        <v>4000</v>
       </c>
       <c r="S21" t="n">
-        <v>383000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>정치적 발언 및 특정 지역 투자 반대 의견 표출. 반도체 산업 및 국가 경제에 대한 부정적 전망 제시.</t>
+          <t>공매도 세력의 개입 및 외인 매도 추정. 단기 급등 후 하락 전환 가능성 제기. 목표가 15000원 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '경제']</t>
+          <t>['공매도', '외인 매도', '단기 급등']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1447000</v>
+        <v>230000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.84%</t>
+          <t>'-8.18%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="G22" t="n">
-        <v>1941</v>
+        <v>1765</v>
       </c>
       <c r="H22" t="n">
-        <v>49.41</v>
+        <v>46.3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1605000</v>
+        <v>250500</v>
       </c>
       <c r="K22" t="n">
-        <v>1538000</v>
+        <v>241500</v>
       </c>
       <c r="L22" t="n">
-        <v>1554000</v>
+        <v>244000</v>
       </c>
       <c r="M22" t="n">
-        <v>1445000</v>
+        <v>228000</v>
       </c>
       <c r="N22" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="O22" t="n">
-        <v>4956494409500</v>
+        <v>3795669348000</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q22" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R22" t="n">
-        <v>-1103000</v>
+        <v>-4524000</v>
       </c>
       <c r="S22" t="n">
-        <v>137000</v>
+        <v>383000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 여론 형성. 반도체 공장 건설 및 정부 정책에 대한 비판적 시각.</t>
+          <t>특정 정치인 및 정부 정책에 대한 부정적 평가가 지배적. 반도체 산업 전망 및 국민연금 우려 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '정치', '공장']</t>
+          <t>['정치인', '반도체 산업', '정부 정책']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2487,6 +2487,98 @@
         </is>
       </c>
       <c r="Z22" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1441000</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-10.22%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E23" t="n">
+        <v>800</v>
+      </c>
+      <c r="F23" t="n">
+        <v>574</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1779</v>
+      </c>
+      <c r="H23" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1437000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5127158708500</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1103000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>137000</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 연계된 부정적 여론 형성. 호남반도체 프로젝트 철회 요구 및 정부 정책 비판.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['정치적 이슈', '호남반도체', '정부 정책']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
